--- a/src/test/resources/testdata/Modules/08_SendBusinessCard/SendBusinessCard/01_SendBusinessCardTest.xlsx
+++ b/src/test/resources/testdata/Modules/08_SendBusinessCard/SendBusinessCard/01_SendBusinessCardTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\08_SendBusinessCard\SendBusinessCard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61153A9-6CB0-4B22-9797-E9B4C7954B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02CBB75-1836-49F8-AD74-F0E53B45C0E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -111,9 +111,6 @@
   </si>
   <si>
     <t>1111</t>
-  </si>
-  <si>
-    <t>Enter Mobile Number to send Digital card.</t>
   </si>
   <si>
     <t>SendBusinessCardTest_04</t>
@@ -191,6 +188,9 @@
 enterotp
 hidekeyboard
 clickonotpsubmitbtn</t>
+  </si>
+  <si>
+    <t>Enter mobile number to send business card</t>
   </si>
 </sst>
 </file>
@@ -801,7 +801,7 @@
       <c r="H4" s="12"/>
       <c r="I4" s="13"/>
       <c r="J4" s="6" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>17</v>
@@ -815,20 +815,20 @@
         <v>12</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="14" t="s">
         <v>29</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>30</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
       <c r="I5" s="13"/>
       <c r="J5" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>17</v>
@@ -842,22 +842,22 @@
         <v>12</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="14" t="s">
         <v>33</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>34</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
       <c r="H6" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I6" s="13"/>
       <c r="J6" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>17</v>
@@ -871,22 +871,22 @@
         <v>12</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="14" t="s">
         <v>38</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>39</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
       <c r="H7" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I7" s="13"/>
       <c r="J7" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>17</v>
@@ -900,26 +900,26 @@
         <v>12</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>43</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>44</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>26</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I8" s="13"/>
       <c r="J8" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>17</v>

--- a/src/test/resources/testdata/Modules/08_SendBusinessCard/SendBusinessCard/01_SendBusinessCardTest.xlsx
+++ b/src/test/resources/testdata/Modules/08_SendBusinessCard/SendBusinessCard/01_SendBusinessCardTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\08_SendBusinessCard\SendBusinessCard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02CBB75-1836-49F8-AD74-F0E53B45C0E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143165A9-8C79-4A48-A24F-2158C75966C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -190,7 +190,7 @@
 clickonotpsubmitbtn</t>
   </si>
   <si>
-    <t>Enter mobile number to send business card</t>
+    <t>Enter Mobile Number to send Digital card.</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/testdata/Modules/08_SendBusinessCard/SendBusinessCard/01_SendBusinessCardTest.xlsx
+++ b/src/test/resources/testdata/Modules/08_SendBusinessCard/SendBusinessCard/01_SendBusinessCardTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\08_SendBusinessCard\SendBusinessCard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143165A9-8C79-4A48-A24F-2158C75966C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD0828B-2C57-45EA-A573-08C00860187B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -190,7 +190,7 @@
 clickonotpsubmitbtn</t>
   </si>
   <si>
-    <t>Enter Mobile Number to send Digital card.</t>
+    <t>Enter mobile number to send business card</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/testdata/Modules/08_SendBusinessCard/SendBusinessCard/01_SendBusinessCardTest.xlsx
+++ b/src/test/resources/testdata/Modules/08_SendBusinessCard/SendBusinessCard/01_SendBusinessCardTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\08_SendBusinessCard\SendBusinessCard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD0828B-2C57-45EA-A573-08C00860187B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF8740C-D496-4A3F-AC3E-20807E10C9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -190,7 +190,7 @@
 clickonotpsubmitbtn</t>
   </si>
   <si>
-    <t>Enter mobile number to send business card</t>
+    <t>Enter Mobile Number to send Digital card.</t>
   </si>
 </sst>
 </file>
